--- a/research/traditional_assets/database/data/thailand/thailand_paper_forest_products.xlsx
+++ b/research/traditional_assets/database/data/thailand/thailand_paper_forest_products.xlsx
@@ -588,118 +588,118 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0576</v>
+        <v>0.0401</v>
       </c>
       <c r="G2">
-        <v>0.1948228882833787</v>
+        <v>0.004703087885985748</v>
       </c>
       <c r="H2">
-        <v>0.1948228882833787</v>
+        <v>0.004703087885985748</v>
       </c>
       <c r="I2">
-        <v>-0.01594005449591281</v>
+        <v>-0.08788598574821853</v>
       </c>
       <c r="J2">
-        <v>-0.01594005449591281</v>
+        <v>-0.08788598574821853</v>
       </c>
       <c r="K2">
-        <v>-17.7</v>
+        <v>-23.7</v>
       </c>
       <c r="L2">
-        <v>-0.1205722070844687</v>
+        <v>-0.1876484560570071</v>
       </c>
       <c r="M2">
-        <v>1.572</v>
+        <v>0.829</v>
       </c>
       <c r="N2">
-        <v>0.013886925795053</v>
+        <v>0.007037351443123938</v>
       </c>
       <c r="O2">
-        <v>-0.0888135593220339</v>
+        <v>-0.0349789029535865</v>
       </c>
       <c r="P2">
-        <v>0.8009999999999999</v>
+        <v>0.829</v>
       </c>
       <c r="Q2">
-        <v>0.007075971731448762</v>
+        <v>0.007037351443123938</v>
       </c>
       <c r="R2">
-        <v>-0.04525423728813559</v>
+        <v>-0.0349789029535865</v>
       </c>
       <c r="S2">
-        <v>0.7710000000000001</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.4904580152671756</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>13</v>
+        <v>12.6</v>
       </c>
       <c r="V2">
-        <v>0.1148409893992933</v>
+        <v>0.1069609507640068</v>
       </c>
       <c r="W2">
-        <v>-0.328996282527881</v>
+        <v>-0.5290178571428572</v>
       </c>
       <c r="X2">
-        <v>0.1968828431496239</v>
+        <v>0.1521888253487968</v>
       </c>
       <c r="Y2">
-        <v>-0.5258791256775049</v>
+        <v>-0.6812066824916541</v>
       </c>
       <c r="Z2">
-        <v>0.5839299920445505</v>
+        <v>0.5465166594547815</v>
       </c>
       <c r="AA2">
-        <v>-0.009307875894988066</v>
+        <v>-0.04803115534400692</v>
       </c>
       <c r="AB2">
-        <v>0.1093588261887583</v>
+        <v>0.08920498642594471</v>
       </c>
       <c r="AC2">
-        <v>-0.1186667020837464</v>
+        <v>-0.1372361417699516</v>
       </c>
       <c r="AD2">
-        <v>199.3</v>
+        <v>214.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>199.3</v>
+        <v>214.5</v>
       </c>
       <c r="AG2">
-        <v>186.3</v>
+        <v>201.9</v>
       </c>
       <c r="AH2">
-        <v>0.63776</v>
+        <v>0.6455010532651219</v>
       </c>
       <c r="AI2">
-        <v>0.8205022643062989</v>
+        <v>0.8841714756801319</v>
       </c>
       <c r="AJ2">
-        <v>0.6220367278797997</v>
+        <v>0.6315295589615265</v>
       </c>
       <c r="AK2">
-        <v>0.8103523270987386</v>
+        <v>0.8778260869565218</v>
       </c>
       <c r="AL2">
-        <v>5.42</v>
+        <v>13</v>
       </c>
       <c r="AM2">
-        <v>5.403</v>
+        <v>12.694</v>
       </c>
       <c r="AN2">
-        <v>18.80188679245283</v>
+        <v>64.60843373493977</v>
       </c>
       <c r="AO2">
-        <v>-0.4317343173431734</v>
+        <v>-0.8538461538461538</v>
       </c>
       <c r="AP2">
-        <v>17.57547169811321</v>
+        <v>60.8132530120482</v>
       </c>
       <c r="AQ2">
-        <v>-0.4330927262631871</v>
+        <v>-0.8744288640302504</v>
       </c>
     </row>
     <row r="3">
@@ -719,118 +719,118 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0576</v>
+        <v>0.0401</v>
       </c>
       <c r="G3">
-        <v>0.1948228882833787</v>
+        <v>0.004703087885985748</v>
       </c>
       <c r="H3">
-        <v>0.1948228882833787</v>
+        <v>0.004703087885985748</v>
       </c>
       <c r="I3">
-        <v>-0.01594005449591281</v>
+        <v>-0.08788598574821853</v>
       </c>
       <c r="J3">
-        <v>-0.01594005449591281</v>
+        <v>-0.08788598574821853</v>
       </c>
       <c r="K3">
-        <v>-17.7</v>
+        <v>-23.7</v>
       </c>
       <c r="L3">
-        <v>-0.1205722070844687</v>
+        <v>-0.1876484560570071</v>
       </c>
       <c r="M3">
-        <v>1.572</v>
+        <v>0.829</v>
       </c>
       <c r="N3">
-        <v>0.013886925795053</v>
+        <v>0.007037351443123938</v>
       </c>
       <c r="O3">
-        <v>-0.0888135593220339</v>
+        <v>-0.0349789029535865</v>
       </c>
       <c r="P3">
-        <v>0.8009999999999999</v>
+        <v>0.829</v>
       </c>
       <c r="Q3">
-        <v>0.007075971731448762</v>
+        <v>0.007037351443123938</v>
       </c>
       <c r="R3">
-        <v>-0.04525423728813559</v>
+        <v>-0.0349789029535865</v>
       </c>
       <c r="S3">
-        <v>0.7710000000000001</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.4904580152671756</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>13</v>
+        <v>12.6</v>
       </c>
       <c r="V3">
-        <v>0.1148409893992933</v>
+        <v>0.1069609507640068</v>
       </c>
       <c r="W3">
-        <v>-0.328996282527881</v>
+        <v>-0.5290178571428572</v>
       </c>
       <c r="X3">
-        <v>0.1968828431496239</v>
+        <v>0.1521888253487968</v>
       </c>
       <c r="Y3">
-        <v>-0.5258791256775049</v>
+        <v>-0.6812066824916541</v>
       </c>
       <c r="Z3">
-        <v>0.5839299920445505</v>
+        <v>0.5465166594547815</v>
       </c>
       <c r="AA3">
-        <v>-0.009307875894988066</v>
+        <v>-0.04803115534400692</v>
       </c>
       <c r="AB3">
-        <v>0.1093588261887583</v>
+        <v>0.08920498642594471</v>
       </c>
       <c r="AC3">
-        <v>-0.1186667020837464</v>
+        <v>-0.1372361417699516</v>
       </c>
       <c r="AD3">
-        <v>199.3</v>
+        <v>214.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>199.3</v>
+        <v>214.5</v>
       </c>
       <c r="AG3">
-        <v>186.3</v>
+        <v>201.9</v>
       </c>
       <c r="AH3">
-        <v>0.63776</v>
+        <v>0.6455010532651219</v>
       </c>
       <c r="AI3">
-        <v>0.8205022643062989</v>
+        <v>0.8841714756801319</v>
       </c>
       <c r="AJ3">
-        <v>0.6220367278797997</v>
+        <v>0.6315295589615265</v>
       </c>
       <c r="AK3">
-        <v>0.8103523270987386</v>
+        <v>0.8778260869565218</v>
       </c>
       <c r="AL3">
-        <v>5.42</v>
+        <v>13</v>
       </c>
       <c r="AM3">
-        <v>5.403</v>
+        <v>12.694</v>
       </c>
       <c r="AN3">
-        <v>18.80188679245283</v>
+        <v>64.60843373493977</v>
       </c>
       <c r="AO3">
-        <v>-0.4317343173431734</v>
+        <v>-0.8538461538461538</v>
       </c>
       <c r="AP3">
-        <v>17.57547169811321</v>
+        <v>60.8132530120482</v>
       </c>
       <c r="AQ3">
-        <v>-0.4330927262631871</v>
+        <v>-0.8744288640302504</v>
       </c>
     </row>
   </sheetData>
